--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260610.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7,270,583</t>
+          <t>64,614,210</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>64,614,210</t>
+          <t>7,270,583</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>104,005,296</t>
+          <t>1,196,514</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,196,514</t>
+          <t>104,005,296</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,779,275</t>
+          <t>196,502,923</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,675,796</t>
+          <t>1,779,275</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>196,502,923</t>
+          <t>1,675,796</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>20,297,919</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>20,297,919</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
